--- a/Registro de Notebooks.xlsx
+++ b/Registro de Notebooks.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leo\Desktop\SistemaNotebook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FB52EA-D2B8-4EB0-9CA5-D60513B1E3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CAC4CE-F014-4A44-BC6E-03CD7A82503B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="19">
   <si>
     <t>ID_Notebook</t>
   </si>
@@ -40,107 +40,50 @@
     <t>Mueble 133</t>
   </si>
   <si>
-    <t>AR020000862120</t>
-  </si>
-  <si>
-    <t>Bangho133-PC4</t>
-  </si>
-  <si>
-    <t>AR020000868317</t>
-  </si>
-  <si>
-    <t>Bangho133-PC5</t>
-  </si>
-  <si>
-    <t>AR020000739736</t>
-  </si>
-  <si>
-    <t>Bangho133-PC6</t>
-  </si>
-  <si>
-    <t>AR020000862109</t>
-  </si>
-  <si>
-    <t>Bangho133-PC7</t>
-  </si>
-  <si>
-    <t>AR020000739726</t>
-  </si>
-  <si>
-    <t>Bangho133-PC9</t>
-  </si>
-  <si>
-    <t>AR020000862140</t>
-  </si>
-  <si>
-    <t>Bangho133-PC10</t>
-  </si>
-  <si>
-    <t>AR020000868311</t>
-  </si>
-  <si>
-    <t>Bangho133-PC11</t>
-  </si>
-  <si>
-    <t>AR020000868325</t>
-  </si>
-  <si>
-    <t>Bangho133-PC12</t>
-  </si>
-  <si>
-    <t>AR020000868330</t>
-  </si>
-  <si>
-    <t>Bangho133-PC14</t>
-  </si>
-  <si>
-    <t>AR020000868318</t>
-  </si>
-  <si>
-    <t>Bangho133-PC15</t>
-  </si>
-  <si>
-    <t>AR020000739725</t>
-  </si>
-  <si>
-    <t>Bangho133-PC16</t>
-  </si>
-  <si>
-    <t>AR020000739723</t>
-  </si>
-  <si>
-    <t>Bangho133-PC17</t>
-  </si>
-  <si>
-    <t>AR02000868334</t>
-  </si>
-  <si>
-    <t>Bangho133-PC19</t>
-  </si>
-  <si>
     <t>AR02000868323</t>
   </si>
   <si>
     <t>Bangho133-PC20</t>
   </si>
   <si>
-    <t>AR02000739709</t>
-  </si>
-  <si>
-    <t>Bangho133-PC21</t>
-  </si>
-  <si>
-    <t>AR02000862108</t>
-  </si>
-  <si>
-    <t>Bangho133-PC23</t>
+    <t>AR020000868300</t>
+  </si>
+  <si>
+    <t>Bangho133-PC2</t>
+  </si>
+  <si>
+    <t>Bangho133-PC3</t>
+  </si>
+  <si>
+    <t>AR020000739737</t>
+  </si>
+  <si>
+    <t>DELL133-PC9</t>
+  </si>
+  <si>
+    <t>DELL133-PC10</t>
+  </si>
+  <si>
+    <t>DELL133-PC14</t>
+  </si>
+  <si>
+    <t>DELL133-PC11</t>
+  </si>
+  <si>
+    <t>DELL133-PC1</t>
+  </si>
+  <si>
+    <t>DELL133-PC5</t>
+  </si>
+  <si>
+    <t>DELL133-PC26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -158,16 +101,33 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF6"/>
+        <bgColor rgb="FFDEEAF6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD6EE"/>
+        <bgColor rgb="FFBDD6EE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -176,17 +136,72 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFC4C7C5"/>
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FFC4C7C5"/>
+        <color indexed="64"/>
       </right>
-      <top style="thin">
-        <color rgb="FFC4C7C5"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color rgb="FFC4C7C5"/>
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -194,15 +209,144 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEEAF6"/>
+          <bgColor rgb="FFDEEAF6"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFDEEAF6"/>
+          <bgColor rgb="FFDEEAF6"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -222,8 +366,8 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Notebooks-style" pivot="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="secondRowStripe" dxfId="0"/>
+      <tableStyleElement type="firstRowStripe" dxfId="7"/>
+      <tableStyleElement type="secondRowStripe" dxfId="6"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -238,12 +382,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B2:C18" headerRowCount="0">
-  <tableColumns count="2">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Column1"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Column2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C3AC6958-6B01-45B8-98F5-FBEB577E145A}" name="Tabla1" displayName="Tabla1" ref="A1:C12" totalsRowShown="0" headerRowBorderDxfId="4" tableBorderDxfId="5" totalsRowBorderDxfId="3">
+  <autoFilter ref="A1:C12" xr:uid="{C3AC6958-6B01-45B8-98F5-FBEB577E145A}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{CCD6AA3D-5196-4628-82DD-FD4A10C37A69}" name="ID_Notebook" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{49BBF196-F9B9-4BC0-BF4C-25D346B56846}" name="Marca y equipo" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{C8D9641B-3582-4A35-946A-8F5BE40586BA}" name="Ubicacion" dataDxfId="2"/>
   </tableColumns>
-  <tableStyleInfo name="Notebooks-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -448,212 +594,147 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.36328125" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="20.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="9">
+        <v>25509981351</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A7" s="9">
+        <v>5072413863</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A8" s="10">
+        <v>414696692583</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C8" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A9" s="9">
+        <v>5348012151</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A7" s="2" t="s">
+      <c r="C9" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A10" s="9">
+        <v>2230503591</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A11" s="9">
+        <v>34816733607</v>
+      </c>
+      <c r="B11" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A9" s="2" t="s">
+      <c r="C11" s="5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A12" s="11">
+        <v>7009011111</v>
+      </c>
+      <c r="B12" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A11" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A13" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A14" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A16" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C18" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
